--- a/artfynd/A 17057-2025 artfynd.xlsx
+++ b/artfynd/A 17057-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111525193</v>
+        <v>104308237</v>
       </c>
       <c r="B2" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Värsjön, väst, Vrm</t>
+          <t>Väst Värsjön, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405150.7483589996</v>
+        <v>405530</v>
       </c>
       <c r="R2" t="n">
-        <v>6707575.375784342</v>
+        <v>6707853</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111525201</v>
+        <v>112552441</v>
       </c>
       <c r="B3" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Värsjön, väst, Vrm</t>
+          <t>Norr Skarptjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405021.5536740309</v>
+        <v>405141</v>
       </c>
       <c r="R3" t="n">
-        <v>6707544.749629043</v>
+        <v>6707610</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +849,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,49 +866,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111525200</v>
+        <v>111525198</v>
       </c>
       <c r="B4" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405067.1064328759</v>
+        <v>405105</v>
       </c>
       <c r="R4" t="n">
-        <v>6707568.203688746</v>
+        <v>6707579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +946,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,50 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111525199</v>
+        <v>112243583</v>
       </c>
       <c r="B5" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Värsjön, väst, Vrm</t>
+          <t>Väst Värsjön, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405066.1712314654</v>
+        <v>405092</v>
       </c>
       <c r="R5" t="n">
-        <v>6707570.20025613</v>
+        <v>6707543</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1043,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,62 +1060,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111525196</v>
+        <v>112243593</v>
       </c>
       <c r="B6" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Värsjön, väst, Vrm</t>
+          <t>Väst Värsjön, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405149.8648065196</v>
+        <v>405023</v>
       </c>
       <c r="R6" t="n">
-        <v>6707579.342975553</v>
+        <v>6707451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1140,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,62 +1157,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111525197</v>
+        <v>112243599</v>
       </c>
       <c r="B7" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Värsjön, väst, Vrm</t>
+          <t>Väst Värsjön, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405103.0112066023</v>
+        <v>405123</v>
       </c>
       <c r="R7" t="n">
-        <v>6707581.558304227</v>
+        <v>6707479</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1237,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,31 +1254,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111525198</v>
+        <v>112552422</v>
       </c>
       <c r="B8" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1383,14 +1297,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Värsjön, väst, Vrm</t>
+          <t>Norr Skarptjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405104.9075025823</v>
+        <v>405142</v>
       </c>
       <c r="R8" t="n">
-        <v>6707578.550527018</v>
+        <v>6707611</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1334,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,62 +1351,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111525194</v>
+        <v>112552431</v>
       </c>
       <c r="B9" t="n">
-        <v>78081</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Värsjön, väst, Vrm</t>
+          <t>Norr Skarptjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405155.8122676918</v>
+        <v>405092</v>
       </c>
       <c r="R9" t="n">
-        <v>6707580.17297498</v>
+        <v>6707547</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1431,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,62 +1448,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111525195</v>
+        <v>112552450</v>
       </c>
       <c r="B10" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Värsjön, väst, Vrm</t>
+          <t>Norr Skarptjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405148.164706406</v>
+        <v>405217</v>
       </c>
       <c r="R10" t="n">
-        <v>6707571.006534745</v>
+        <v>6707522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1528,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,62 +1545,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112243576</v>
+        <v>112552456</v>
       </c>
       <c r="B11" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väst Värsjön, Vrm</t>
+          <t>Norr Skarptjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405113</v>
+        <v>405106</v>
       </c>
       <c r="R11" t="n">
-        <v>6707478</v>
+        <v>6707515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,62 +1642,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112243579</v>
+        <v>117427824</v>
       </c>
       <c r="B12" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väst Värsjön, Vrm</t>
+          <t>Olasbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405038</v>
+        <v>405246</v>
       </c>
       <c r="R12" t="n">
-        <v>6707565</v>
+        <v>6707733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,12 +1722,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,33 +1736,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112243599</v>
+        <v>111525195</v>
       </c>
       <c r="B13" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,34 +1766,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väst Värsjön, Vrm</t>
+          <t>Värsjön, väst, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405123</v>
+        <v>405148</v>
       </c>
       <c r="R13" t="n">
-        <v>6707479</v>
+        <v>6707571</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,27 +1840,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112243593</v>
+        <v>111525193</v>
       </c>
       <c r="B14" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,34 +1863,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väst Värsjön, Vrm</t>
+          <t>Värsjön, väst, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405024</v>
+        <v>405151</v>
       </c>
       <c r="R14" t="n">
-        <v>6707451</v>
+        <v>6707575</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,27 +1937,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112243583</v>
+        <v>111525197</v>
       </c>
       <c r="B15" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,34 +1960,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väst Värsjön, Vrm</t>
+          <t>Värsjön, väst, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405093</v>
+        <v>405103</v>
       </c>
       <c r="R15" t="n">
-        <v>6707542</v>
+        <v>6707582</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,27 +2034,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112552441</v>
+        <v>111525199</v>
       </c>
       <c r="B16" t="n">
-        <v>89681</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,43 +2057,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norr Skarptjärnen, Vrm</t>
+          <t>Värsjön, väst, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405140</v>
+        <v>405066</v>
       </c>
       <c r="R16" t="n">
-        <v>6707610</v>
+        <v>6707570</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,27 +2131,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112552456</v>
+        <v>111525201</v>
       </c>
       <c r="B17" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,34 +2154,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norr Skarptjärnen, Vrm</t>
+          <t>Värsjön, väst, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405106</v>
+        <v>405021</v>
       </c>
       <c r="R17" t="n">
-        <v>6707515</v>
+        <v>6707545</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,27 +2228,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112552431</v>
+        <v>112243576</v>
       </c>
       <c r="B18" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,34 +2251,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norr Skarptjärnen, Vrm</t>
+          <t>Väst Värsjön, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405092</v>
+        <v>405113</v>
       </c>
       <c r="R18" t="n">
-        <v>6707546</v>
+        <v>6707478</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,27 +2325,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112552422</v>
+        <v>112243579</v>
       </c>
       <c r="B19" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,34 +2348,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norr Skarptjärnen, Vrm</t>
+          <t>Väst Värsjön, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405141</v>
+        <v>405038</v>
       </c>
       <c r="R19" t="n">
-        <v>6707611</v>
+        <v>6707565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,15 +2422,403 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>111525196</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Värsjön, väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>405150</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6707579</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>111525200</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Värsjön, väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>405067</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6707568</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>112243605</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Väst Värsjön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>404979</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6707515</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>111525194</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Värsjön, väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>405156</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6707580</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17057-2025 artfynd.xlsx
+++ b/artfynd/A 17057-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308237</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552441</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525198</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243583</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243593</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243599</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552422</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552431</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552450</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552456</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1752,6 +1807,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117427824</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,6 +1909,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525195</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525193</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2043,6 +2113,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525197</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2140,6 +2215,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525199</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2237,6 +2317,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525201</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2334,6 +2419,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243576</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2431,6 +2521,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243579</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2528,6 +2623,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525196</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2625,6 +2725,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525200</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2722,6 +2827,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243605</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2819,8 +2929,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525194</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>